--- a/data/labour-market/Employment rate/employment_rate_geographical_10022026.xlsx
+++ b/data/labour-market/Employment rate/employment_rate_geographical_10022026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/files/IPR/Centres/Brunel Centre/Labour Market/Employment_rate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\IPR\Centres\Brunel Centre\Labour Market\Employment_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B418E9-9B6D-F14E-A36D-597EC9824C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B72217-1B5A-464C-B471-ACCD39645AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6060" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{F3838E48-33B6-3E4D-ABD2-7FEC8AC3400F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F3838E48-33B6-3E4D-ABD2-7FEC8AC3400F}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <t>Office for National Statistics (ONS)</t>
   </si>
   <si>
-    <t>The Greater West of England Area (Bristol, Bath &amp; North East Somerset, South Gloucestershire, North Somerset, Swindon, Wiltshire) and individual local authorities, England and United Kingdom (+excluding London)</t>
-  </si>
-  <si>
     <t>Aggregated by NOMIS</t>
   </si>
   <si>
@@ -209,6 +206,9 @@
   </si>
   <si>
     <t>employment_rate</t>
+  </si>
+  <si>
+    <t>The Greater West of England Area (Bristol, Bath &amp; North East Somerset, Gloucestershire, South Gloucestershire, North Somerset, Swindon, Wiltshire) and individual local authorities, England and United Kingdom (+excluding London)</t>
   </si>
 </sst>
 </file>
@@ -281,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -313,6 +313,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -649,13 +652,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF34F89D-D895-144E-9321-FCBFF913ABF8}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="2" width="54.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -663,28 +666,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -692,15 +695,15 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -708,34 +711,34 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="64" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B9" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="80" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
-        <v>32</v>
+      <c r="B11" s="15" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -746,61 +749,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F31F01-CF34-B04B-8F44-AFC33149FAE8}">
   <dimension ref="A1:BI105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1" collapsed="1"/>
     <col min="2" max="61" width="14" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:46" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:46" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
@@ -837,9 +840,9 @@
       <c r="AS8" s="9"/>
       <c r="AT8" s="9"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="7">
         <v>93100</v>
@@ -888,9 +891,9 @@
       <c r="AS9" s="10"/>
       <c r="AT9" s="10"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="7">
         <v>255600</v>
@@ -939,9 +942,9 @@
       <c r="AS10" s="10"/>
       <c r="AT10" s="10"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="7">
         <v>310400</v>
@@ -990,9 +993,9 @@
       <c r="AS11" s="10"/>
       <c r="AT11" s="10"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="7">
         <v>101900</v>
@@ -1041,9 +1044,9 @@
       <c r="AS12" s="10"/>
       <c r="AT12" s="10"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="7">
         <v>148900</v>
@@ -1092,9 +1095,9 @@
       <c r="AS13" s="10"/>
       <c r="AT13" s="10"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="7">
         <v>108400</v>
@@ -1143,9 +1146,9 @@
       <c r="AS14" s="10"/>
       <c r="AT14" s="10"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7">
         <v>245900</v>
@@ -1194,9 +1197,9 @@
       <c r="AS15" s="10"/>
       <c r="AT15" s="10"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="7">
         <v>1264300</v>
@@ -1245,9 +1248,9 @@
       <c r="AS16" s="10"/>
       <c r="AT16" s="10"/>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="7">
         <v>31631100</v>
@@ -1296,9 +1299,9 @@
       <c r="AS17" s="10"/>
       <c r="AT17" s="10"/>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="7">
         <v>26941500</v>
@@ -1347,7 +1350,7 @@
       <c r="AS18" s="10"/>
       <c r="AT18" s="10"/>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.4">
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="7"/>
@@ -1383,9 +1386,9 @@
       <c r="AS19" s="10"/>
       <c r="AT19" s="10"/>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
@@ -1422,7 +1425,7 @@
       <c r="AS20" s="10"/>
       <c r="AT20" s="10"/>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="7"/>
@@ -1470,7 +1473,7 @@
       <c r="AS21" s="10"/>
       <c r="AT21" s="10"/>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="7"/>
@@ -1518,7 +1521,7 @@
       <c r="AS22" s="10"/>
       <c r="AT22" s="10"/>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="7"/>
@@ -1566,7 +1569,7 @@
       <c r="AS23" s="10"/>
       <c r="AT23" s="10"/>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="7"/>
@@ -1614,7 +1617,7 @@
       <c r="AS24" s="10"/>
       <c r="AT24" s="10"/>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="7"/>
@@ -1662,7 +1665,7 @@
       <c r="AS25" s="10"/>
       <c r="AT25" s="10"/>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="7"/>
@@ -1710,7 +1713,7 @@
       <c r="AS26" s="10"/>
       <c r="AT26" s="10"/>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="7"/>
@@ -1758,7 +1761,7 @@
       <c r="AS27" s="10"/>
       <c r="AT27" s="10"/>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A28" s="5"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1821,7 +1824,7 @@
       <c r="BH28" s="10"/>
       <c r="BI28" s="10"/>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A29" s="5"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1884,34 +1887,34 @@
       <c r="BH29" s="10"/>
       <c r="BI29" s="10"/>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A33" s="4"/>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A37" s="4"/>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
     </row>
-    <row r="43" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="6"/>
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
@@ -1974,7 +1977,7 @@
       <c r="BH43" s="14"/>
       <c r="BI43" s="14"/>
     </row>
-    <row r="44" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -2036,7 +2039,7 @@
       <c r="BH44" s="9"/>
       <c r="BI44" s="9"/>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A45" s="5"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -2099,7 +2102,7 @@
       <c r="BH45" s="10"/>
       <c r="BI45" s="10"/>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A46" s="5"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -2162,7 +2165,7 @@
       <c r="BH46" s="10"/>
       <c r="BI46" s="10"/>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A47" s="5"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -2225,7 +2228,7 @@
       <c r="BH47" s="10"/>
       <c r="BI47" s="10"/>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A48" s="5"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -2288,7 +2291,7 @@
       <c r="BH48" s="10"/>
       <c r="BI48" s="10"/>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A49" s="5"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -2351,7 +2354,7 @@
       <c r="BH49" s="10"/>
       <c r="BI49" s="10"/>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A50" s="5"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -2414,7 +2417,7 @@
       <c r="BH50" s="10"/>
       <c r="BI50" s="10"/>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A51" s="5"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -2477,7 +2480,7 @@
       <c r="BH51" s="10"/>
       <c r="BI51" s="10"/>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A52" s="5"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -2540,7 +2543,7 @@
       <c r="BH52" s="10"/>
       <c r="BI52" s="10"/>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A53" s="5"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -2603,7 +2606,7 @@
       <c r="BH53" s="10"/>
       <c r="BI53" s="10"/>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A54" s="5"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -2666,7 +2669,7 @@
       <c r="BH54" s="10"/>
       <c r="BI54" s="10"/>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A55" s="5"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -2729,7 +2732,7 @@
       <c r="BH55" s="10"/>
       <c r="BI55" s="10"/>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A56" s="5"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -2792,7 +2795,7 @@
       <c r="BH56" s="10"/>
       <c r="BI56" s="10"/>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A57" s="5"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -2855,7 +2858,7 @@
       <c r="BH57" s="10"/>
       <c r="BI57" s="10"/>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A58" s="5"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -2918,7 +2921,7 @@
       <c r="BH58" s="10"/>
       <c r="BI58" s="10"/>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A59" s="5"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -2981,7 +2984,7 @@
       <c r="BH59" s="10"/>
       <c r="BI59" s="10"/>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A60" s="5"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -3044,7 +3047,7 @@
       <c r="BH60" s="10"/>
       <c r="BI60" s="10"/>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A61" s="5"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -3107,7 +3110,7 @@
       <c r="BH61" s="10"/>
       <c r="BI61" s="10"/>
     </row>
-    <row r="62" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A62" s="5"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -3170,7 +3173,7 @@
       <c r="BH62" s="10"/>
       <c r="BI62" s="10"/>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A63" s="5"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -3233,7 +3236,7 @@
       <c r="BH63" s="10"/>
       <c r="BI63" s="10"/>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A64" s="5"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -3296,7 +3299,7 @@
       <c r="BH64" s="10"/>
       <c r="BI64" s="10"/>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A65" s="5"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -3359,34 +3362,34 @@
       <c r="BH65" s="10"/>
       <c r="BI65" s="10"/>
     </row>
-    <row r="67" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A67" s="4"/>
     </row>
-    <row r="68" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A68" s="4"/>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A69" s="4"/>
     </row>
-    <row r="72" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A72" s="3"/>
     </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A73" s="4"/>
     </row>
-    <row r="75" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
     </row>
-    <row r="76" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
     </row>
-    <row r="77" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
     </row>
-    <row r="79" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="6"/>
       <c r="B79" s="13"/>
       <c r="C79" s="14"/>
@@ -3449,7 +3452,7 @@
       <c r="BH79" s="14"/>
       <c r="BI79" s="14"/>
     </row>
-    <row r="80" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:61" ht="26" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
@@ -3511,7 +3514,7 @@
       <c r="BH80" s="9"/>
       <c r="BI80" s="9"/>
     </row>
-    <row r="81" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A81" s="5"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -3574,7 +3577,7 @@
       <c r="BH81" s="10"/>
       <c r="BI81" s="10"/>
     </row>
-    <row r="82" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A82" s="5"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -3637,7 +3640,7 @@
       <c r="BH82" s="10"/>
       <c r="BI82" s="10"/>
     </row>
-    <row r="83" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A83" s="5"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -3700,7 +3703,7 @@
       <c r="BH83" s="10"/>
       <c r="BI83" s="10"/>
     </row>
-    <row r="84" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A84" s="5"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -3763,7 +3766,7 @@
       <c r="BH84" s="10"/>
       <c r="BI84" s="10"/>
     </row>
-    <row r="85" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A85" s="5"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -3826,7 +3829,7 @@
       <c r="BH85" s="10"/>
       <c r="BI85" s="10"/>
     </row>
-    <row r="86" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A86" s="5"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -3889,7 +3892,7 @@
       <c r="BH86" s="10"/>
       <c r="BI86" s="10"/>
     </row>
-    <row r="87" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A87" s="5"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -3952,7 +3955,7 @@
       <c r="BH87" s="10"/>
       <c r="BI87" s="10"/>
     </row>
-    <row r="88" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A88" s="5"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -4015,7 +4018,7 @@
       <c r="BH88" s="10"/>
       <c r="BI88" s="10"/>
     </row>
-    <row r="89" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A89" s="5"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -4078,7 +4081,7 @@
       <c r="BH89" s="10"/>
       <c r="BI89" s="10"/>
     </row>
-    <row r="90" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A90" s="5"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -4141,7 +4144,7 @@
       <c r="BH90" s="10"/>
       <c r="BI90" s="10"/>
     </row>
-    <row r="91" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A91" s="5"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -4204,7 +4207,7 @@
       <c r="BH91" s="10"/>
       <c r="BI91" s="10"/>
     </row>
-    <row r="92" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A92" s="5"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -4267,7 +4270,7 @@
       <c r="BH92" s="10"/>
       <c r="BI92" s="10"/>
     </row>
-    <row r="93" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A93" s="5"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -4330,7 +4333,7 @@
       <c r="BH93" s="10"/>
       <c r="BI93" s="10"/>
     </row>
-    <row r="94" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A94" s="5"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -4393,7 +4396,7 @@
       <c r="BH94" s="10"/>
       <c r="BI94" s="10"/>
     </row>
-    <row r="95" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A95" s="5"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -4456,7 +4459,7 @@
       <c r="BH95" s="10"/>
       <c r="BI95" s="10"/>
     </row>
-    <row r="96" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A96" s="5"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -4519,7 +4522,7 @@
       <c r="BH96" s="10"/>
       <c r="BI96" s="10"/>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A97" s="5"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -4582,7 +4585,7 @@
       <c r="BH97" s="10"/>
       <c r="BI97" s="10"/>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A98" s="5"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -4645,7 +4648,7 @@
       <c r="BH98" s="10"/>
       <c r="BI98" s="10"/>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A99" s="5"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -4708,7 +4711,7 @@
       <c r="BH99" s="10"/>
       <c r="BI99" s="10"/>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A100" s="5"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -4771,7 +4774,7 @@
       <c r="BH100" s="10"/>
       <c r="BI100" s="10"/>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A101" s="5"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -4834,41 +4837,17 @@
       <c r="BH101" s="10"/>
       <c r="BI101" s="10"/>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A103" s="4"/>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A104" s="4"/>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.4">
       <c r="A105" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="N43:Q43"/>
-    <mergeCell ref="R43:U43"/>
-    <mergeCell ref="V43:Y43"/>
-    <mergeCell ref="Z43:AC43"/>
-    <mergeCell ref="BB43:BE43"/>
-    <mergeCell ref="BF43:BI43"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="N79:Q79"/>
-    <mergeCell ref="R79:U79"/>
-    <mergeCell ref="V79:Y79"/>
-    <mergeCell ref="Z79:AC79"/>
-    <mergeCell ref="AD79:AG79"/>
-    <mergeCell ref="AD43:AG43"/>
-    <mergeCell ref="AH43:AK43"/>
-    <mergeCell ref="AL43:AO43"/>
-    <mergeCell ref="AP43:AS43"/>
-    <mergeCell ref="AT43:AW43"/>
-    <mergeCell ref="AX43:BA43"/>
     <mergeCell ref="BF79:BI79"/>
     <mergeCell ref="AH79:AK79"/>
     <mergeCell ref="AL79:AO79"/>
@@ -4876,6 +4855,30 @@
     <mergeCell ref="AT79:AW79"/>
     <mergeCell ref="AX79:BA79"/>
     <mergeCell ref="BB79:BE79"/>
+    <mergeCell ref="V79:Y79"/>
+    <mergeCell ref="Z79:AC79"/>
+    <mergeCell ref="AD79:AG79"/>
+    <mergeCell ref="AD43:AG43"/>
+    <mergeCell ref="AH43:AK43"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="N79:Q79"/>
+    <mergeCell ref="R79:U79"/>
+    <mergeCell ref="R43:U43"/>
+    <mergeCell ref="V43:Y43"/>
+    <mergeCell ref="Z43:AC43"/>
+    <mergeCell ref="BB43:BE43"/>
+    <mergeCell ref="BF43:BI43"/>
+    <mergeCell ref="AL43:AO43"/>
+    <mergeCell ref="AP43:AS43"/>
+    <mergeCell ref="AT43:AW43"/>
+    <mergeCell ref="AX43:BA43"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="N43:Q43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4884,7 +4887,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBF1B92-E1FB-E74A-B3FF-5116134587D5}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -4898,7 +4901,7 @@
     <col min="11" max="11" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4906,21 +4909,21 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
       <c r="E1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="7">
         <v>93100</v>
@@ -4932,12 +4935,12 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" s="7">
         <v>255600</v>
@@ -4949,12 +4952,12 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="7">
         <v>310400</v>
@@ -4966,12 +4969,12 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="7">
         <v>101900</v>
@@ -4983,12 +4986,12 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="7">
         <v>148900</v>
@@ -5000,12 +5003,12 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="7">
         <v>108400</v>
@@ -5017,12 +5020,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="7">
         <v>245900</v>
@@ -5034,9 +5037,9 @@
         <v>82.6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>3</v>
@@ -5051,9 +5054,9 @@
         <v>80.400000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>4</v>
@@ -5068,9 +5071,9 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>4</v>
@@ -5085,131 +5088,131 @@
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
     </row>
